--- a/artfynd/A 49990-2023 artfynd.xlsx
+++ b/artfynd/A 49990-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -935,6 +935,732 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122249139</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56277</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sydöstra Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>654697</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6630371</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inventering för Uppsala kommun</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122249179</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56263</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sydöstra Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>654759</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6630339</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Inventering för Uppsala kommun</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122249133</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56277</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sydöstra Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>654716</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6630357</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Inventering för Uppsala kommun</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122249134</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56277</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sydöstra Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>654696</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6630370</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Inventering för Uppsala kommun</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122249131</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56277</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sydöstra Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>654693</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6630371</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Inventering för Uppsala kommun</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122249138</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56277</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sydöstra Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>654707</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6630361</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Inventering för Uppsala kommun</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49990-2023 artfynd.xlsx
+++ b/artfynd/A 49990-2023 artfynd.xlsx
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122249139</v>
+        <v>122249133</v>
       </c>
       <c r="B4" t="n">
-        <v>56277</v>
+        <v>56278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654697</v>
+        <v>654716</v>
       </c>
       <c r="R4" t="n">
-        <v>6630371</v>
+        <v>6630357</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122249179</v>
+        <v>122249138</v>
       </c>
       <c r="B5" t="n">
-        <v>56263</v>
+        <v>56278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,25 +1070,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654759</v>
+        <v>654707</v>
       </c>
       <c r="R5" t="n">
-        <v>6630339</v>
+        <v>6630361</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1172,17 +1172,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122249133</v>
+        <v>122249134</v>
       </c>
       <c r="B6" t="n">
-        <v>56277</v>
+        <v>56278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654716</v>
+        <v>654696</v>
       </c>
       <c r="R6" t="n">
-        <v>6630357</v>
+        <v>6630370</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122249134</v>
+        <v>122249131</v>
       </c>
       <c r="B7" t="n">
-        <v>56277</v>
+        <v>56278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654696</v>
+        <v>654693</v>
       </c>
       <c r="R7" t="n">
-        <v>6630370</v>
+        <v>6630371</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1421,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122249131</v>
+        <v>122249179</v>
       </c>
       <c r="B8" t="n">
-        <v>56277</v>
+        <v>56264</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,25 +1433,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654693</v>
+        <v>654759</v>
       </c>
       <c r="R8" t="n">
-        <v>6630371</v>
+        <v>6630339</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1535,17 +1535,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249138</v>
+        <v>122249139</v>
       </c>
       <c r="B9" t="n">
-        <v>56277</v>
+        <v>56278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654707</v>
+        <v>654697</v>
       </c>
       <c r="R9" t="n">
-        <v>6630361</v>
+        <v>6630371</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 49990-2023 artfynd.xlsx
+++ b/artfynd/A 49990-2023 artfynd.xlsx
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122249133</v>
+        <v>122249131</v>
       </c>
       <c r="B4" t="n">
-        <v>56278</v>
+        <v>56280</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654716</v>
+        <v>654693</v>
       </c>
       <c r="R4" t="n">
-        <v>6630357</v>
+        <v>6630371</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1061,7 +1061,7 @@
         <v>122249138</v>
       </c>
       <c r="B5" t="n">
-        <v>56278</v>
+        <v>56280</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>122249134</v>
       </c>
       <c r="B6" t="n">
-        <v>56278</v>
+        <v>56280</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122249131</v>
+        <v>122249139</v>
       </c>
       <c r="B7" t="n">
-        <v>56278</v>
+        <v>56280</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654693</v>
+        <v>654697</v>
       </c>
       <c r="R7" t="n">
         <v>6630371</v>
@@ -1421,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122249179</v>
+        <v>122249133</v>
       </c>
       <c r="B8" t="n">
-        <v>56264</v>
+        <v>56280</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,25 +1433,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654759</v>
+        <v>654716</v>
       </c>
       <c r="R8" t="n">
-        <v>6630339</v>
+        <v>6630357</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1535,17 +1535,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249139</v>
+        <v>122249179</v>
       </c>
       <c r="B9" t="n">
-        <v>56278</v>
+        <v>56266</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,25 +1554,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654697</v>
+        <v>654759</v>
       </c>
       <c r="R9" t="n">
-        <v>6630371</v>
+        <v>6630339</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 49990-2023 artfynd.xlsx
+++ b/artfynd/A 49990-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122249131</v>
+        <v>122249133</v>
       </c>
       <c r="B4" t="n">
         <v>56280</v>
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654693</v>
+        <v>654716</v>
       </c>
       <c r="R4" t="n">
-        <v>6630371</v>
+        <v>6630357</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122249139</v>
+        <v>122249131</v>
       </c>
       <c r="B7" t="n">
         <v>56280</v>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654697</v>
+        <v>654693</v>
       </c>
       <c r="R7" t="n">
         <v>6630371</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122249133</v>
+        <v>122249139</v>
       </c>
       <c r="B8" t="n">
         <v>56280</v>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654716</v>
+        <v>654697</v>
       </c>
       <c r="R8" t="n">
-        <v>6630357</v>
+        <v>6630371</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 49990-2023 artfynd.xlsx
+++ b/artfynd/A 49990-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122249133</v>
+        <v>122249139</v>
       </c>
       <c r="B4" t="n">
         <v>56280</v>
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654716</v>
+        <v>654697</v>
       </c>
       <c r="R4" t="n">
-        <v>6630357</v>
+        <v>6630371</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122249134</v>
+        <v>122249133</v>
       </c>
       <c r="B5" t="n">
         <v>56280</v>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654696</v>
+        <v>654716</v>
       </c>
       <c r="R5" t="n">
-        <v>6630370</v>
+        <v>6630357</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1179,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122249179</v>
+        <v>122249131</v>
       </c>
       <c r="B6" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,25 +1191,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654759</v>
+        <v>654693</v>
       </c>
       <c r="R6" t="n">
-        <v>6630339</v>
+        <v>6630371</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1293,14 +1293,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122249138</v>
+        <v>122249134</v>
       </c>
       <c r="B7" t="n">
         <v>56280</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654707</v>
+        <v>654696</v>
       </c>
       <c r="R7" t="n">
-        <v>6630361</v>
+        <v>6630370</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122249139</v>
+        <v>122249138</v>
       </c>
       <c r="B8" t="n">
         <v>56280</v>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654697</v>
+        <v>654707</v>
       </c>
       <c r="R8" t="n">
-        <v>6630371</v>
+        <v>6630361</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249131</v>
+        <v>122249179</v>
       </c>
       <c r="B9" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,25 +1554,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654693</v>
+        <v>654759</v>
       </c>
       <c r="R9" t="n">
-        <v>6630371</v>
+        <v>6630339</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 49990-2023 artfynd.xlsx
+++ b/artfynd/A 49990-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122249139</v>
+        <v>122249134</v>
       </c>
       <c r="B4" t="n">
         <v>56280</v>
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654697</v>
+        <v>654696</v>
       </c>
       <c r="R4" t="n">
-        <v>6630371</v>
+        <v>6630370</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122249133</v>
+        <v>122249139</v>
       </c>
       <c r="B5" t="n">
         <v>56280</v>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654716</v>
+        <v>654697</v>
       </c>
       <c r="R5" t="n">
-        <v>6630357</v>
+        <v>6630371</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122249134</v>
+        <v>122249138</v>
       </c>
       <c r="B7" t="n">
         <v>56280</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654696</v>
+        <v>654707</v>
       </c>
       <c r="R7" t="n">
-        <v>6630370</v>
+        <v>6630361</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122249138</v>
+        <v>122249133</v>
       </c>
       <c r="B8" t="n">
         <v>56280</v>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654707</v>
+        <v>654716</v>
       </c>
       <c r="R8" t="n">
-        <v>6630361</v>
+        <v>6630357</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 49990-2023 artfynd.xlsx
+++ b/artfynd/A 49990-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122249134</v>
+        <v>122249138</v>
       </c>
       <c r="B4" t="n">
         <v>56280</v>
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654696</v>
+        <v>654707</v>
       </c>
       <c r="R4" t="n">
-        <v>6630370</v>
+        <v>6630361</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122249138</v>
+        <v>122249134</v>
       </c>
       <c r="B7" t="n">
         <v>56280</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654707</v>
+        <v>654696</v>
       </c>
       <c r="R7" t="n">
-        <v>6630361</v>
+        <v>6630370</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1421,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122249133</v>
+        <v>122249179</v>
       </c>
       <c r="B8" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,25 +1433,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654716</v>
+        <v>654759</v>
       </c>
       <c r="R8" t="n">
-        <v>6630357</v>
+        <v>6630339</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1535,17 +1535,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249179</v>
+        <v>122249133</v>
       </c>
       <c r="B9" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,25 +1554,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654759</v>
+        <v>654716</v>
       </c>
       <c r="R9" t="n">
-        <v>6630339</v>
+        <v>6630357</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 49990-2023 artfynd.xlsx
+++ b/artfynd/A 49990-2023 artfynd.xlsx
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122249138</v>
+        <v>122249134</v>
       </c>
       <c r="B4" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654707</v>
+        <v>654696</v>
       </c>
       <c r="R4" t="n">
-        <v>6630361</v>
+        <v>6630370</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1061,7 +1061,7 @@
         <v>122249139</v>
       </c>
       <c r="B5" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1179,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122249131</v>
+        <v>122249138</v>
       </c>
       <c r="B6" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654693</v>
+        <v>654707</v>
       </c>
       <c r="R6" t="n">
-        <v>6630371</v>
+        <v>6630361</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122249134</v>
+        <v>122249131</v>
       </c>
       <c r="B7" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654696</v>
+        <v>654693</v>
       </c>
       <c r="R7" t="n">
-        <v>6630370</v>
+        <v>6630371</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1421,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122249179</v>
+        <v>122249133</v>
       </c>
       <c r="B8" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,25 +1433,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654759</v>
+        <v>654716</v>
       </c>
       <c r="R8" t="n">
-        <v>6630339</v>
+        <v>6630357</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1535,17 +1535,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249133</v>
+        <v>122249179</v>
       </c>
       <c r="B9" t="n">
-        <v>56280</v>
+        <v>56271</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,25 +1554,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654716</v>
+        <v>654759</v>
       </c>
       <c r="R9" t="n">
-        <v>6630357</v>
+        <v>6630339</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 49990-2023 artfynd.xlsx
+++ b/artfynd/A 49990-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122249134</v>
+        <v>122249131</v>
       </c>
       <c r="B4" t="n">
         <v>56285</v>
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654696</v>
+        <v>654693</v>
       </c>
       <c r="R4" t="n">
-        <v>6630370</v>
+        <v>6630371</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122249139</v>
+        <v>122249138</v>
       </c>
       <c r="B5" t="n">
         <v>56285</v>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654697</v>
+        <v>654707</v>
       </c>
       <c r="R5" t="n">
-        <v>6630371</v>
+        <v>6630361</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122249138</v>
+        <v>122249134</v>
       </c>
       <c r="B6" t="n">
         <v>56285</v>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654707</v>
+        <v>654696</v>
       </c>
       <c r="R6" t="n">
-        <v>6630361</v>
+        <v>6630370</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122249131</v>
+        <v>122249139</v>
       </c>
       <c r="B7" t="n">
         <v>56285</v>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654693</v>
+        <v>654697</v>
       </c>
       <c r="R7" t="n">
         <v>6630371</v>
@@ -1421,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122249133</v>
+        <v>122249179</v>
       </c>
       <c r="B8" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,25 +1433,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654716</v>
+        <v>654759</v>
       </c>
       <c r="R8" t="n">
-        <v>6630357</v>
+        <v>6630339</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1535,17 +1535,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249179</v>
+        <v>122249133</v>
       </c>
       <c r="B9" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,25 +1554,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654759</v>
+        <v>654716</v>
       </c>
       <c r="R9" t="n">
-        <v>6630339</v>
+        <v>6630357</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 49990-2023 artfynd.xlsx
+++ b/artfynd/A 49990-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122249131</v>
+        <v>122249133</v>
       </c>
       <c r="B4" t="n">
         <v>56285</v>
@@ -955,11 +955,6 @@
       <c r="E4" t="n">
         <v>100092</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -991,10 +986,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654693</v>
+        <v>654716</v>
       </c>
       <c r="R4" t="n">
-        <v>6630371</v>
+        <v>6630357</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1058,7 +1053,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122249138</v>
+        <v>122249134</v>
       </c>
       <c r="B5" t="n">
         <v>56285</v>
@@ -1076,11 +1071,6 @@
       <c r="E5" t="n">
         <v>100092</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -1112,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654707</v>
+        <v>654696</v>
       </c>
       <c r="R5" t="n">
-        <v>6630361</v>
+        <v>6630370</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1179,10 +1169,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122249134</v>
+        <v>122249179</v>
       </c>
       <c r="B6" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,25 +1181,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1233,10 +1218,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654696</v>
+        <v>654759</v>
       </c>
       <c r="R6" t="n">
-        <v>6630370</v>
+        <v>6630339</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1293,14 +1278,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122249139</v>
+        <v>122249138</v>
       </c>
       <c r="B7" t="n">
         <v>56285</v>
@@ -1318,11 +1303,6 @@
       <c r="E7" t="n">
         <v>100092</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -1354,10 +1334,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654697</v>
+        <v>654707</v>
       </c>
       <c r="R7" t="n">
-        <v>6630371</v>
+        <v>6630361</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1421,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122249179</v>
+        <v>122249131</v>
       </c>
       <c r="B8" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,25 +1413,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1475,10 +1450,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654759</v>
+        <v>654693</v>
       </c>
       <c r="R8" t="n">
-        <v>6630339</v>
+        <v>6630371</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1535,14 +1510,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249133</v>
+        <v>122249139</v>
       </c>
       <c r="B9" t="n">
         <v>56285</v>
@@ -1560,11 +1535,6 @@
       <c r="E9" t="n">
         <v>100092</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -1596,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654716</v>
+        <v>654697</v>
       </c>
       <c r="R9" t="n">
-        <v>6630357</v>
+        <v>6630371</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 49990-2023 artfynd.xlsx
+++ b/artfynd/A 49990-2023 artfynd.xlsx
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122249133</v>
+        <v>122249131</v>
       </c>
       <c r="B4" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,6 +955,11 @@
       <c r="E4" t="n">
         <v>100092</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -986,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654716</v>
+        <v>654693</v>
       </c>
       <c r="R4" t="n">
-        <v>6630357</v>
+        <v>6630371</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1053,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122249134</v>
+        <v>122249179</v>
       </c>
       <c r="B5" t="n">
-        <v>56285</v>
+        <v>56275</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,20 +1070,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>205998</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1102,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654696</v>
+        <v>654759</v>
       </c>
       <c r="R5" t="n">
-        <v>6630370</v>
+        <v>6630339</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1162,17 +1172,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122249179</v>
+        <v>122249139</v>
       </c>
       <c r="B6" t="n">
-        <v>56271</v>
+        <v>56289</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,20 +1191,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>100092</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1218,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654759</v>
+        <v>654697</v>
       </c>
       <c r="R6" t="n">
-        <v>6630339</v>
+        <v>6630371</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1278,17 +1293,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122249138</v>
+        <v>122249133</v>
       </c>
       <c r="B7" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1303,6 +1318,11 @@
       <c r="E7" t="n">
         <v>100092</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -1334,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654707</v>
+        <v>654716</v>
       </c>
       <c r="R7" t="n">
-        <v>6630361</v>
+        <v>6630357</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1401,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122249131</v>
+        <v>122249134</v>
       </c>
       <c r="B8" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,6 +1439,11 @@
       <c r="E8" t="n">
         <v>100092</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -1450,10 +1475,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654693</v>
+        <v>654696</v>
       </c>
       <c r="R8" t="n">
-        <v>6630371</v>
+        <v>6630370</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1517,10 +1542,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249139</v>
+        <v>122249138</v>
       </c>
       <c r="B9" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1535,6 +1560,11 @@
       <c r="E9" t="n">
         <v>100092</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -1566,10 +1596,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654697</v>
+        <v>654707</v>
       </c>
       <c r="R9" t="n">
-        <v>6630371</v>
+        <v>6630361</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 49990-2023 artfynd.xlsx
+++ b/artfynd/A 49990-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122249131</v>
+        <v>122249134</v>
       </c>
       <c r="B4" t="n">
         <v>56289</v>
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654693</v>
+        <v>654696</v>
       </c>
       <c r="R4" t="n">
-        <v>6630371</v>
+        <v>6630370</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122249179</v>
+        <v>122249139</v>
       </c>
       <c r="B5" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,25 +1070,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654759</v>
+        <v>654697</v>
       </c>
       <c r="R5" t="n">
-        <v>6630339</v>
+        <v>6630371</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1172,14 +1172,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122249139</v>
+        <v>122249133</v>
       </c>
       <c r="B6" t="n">
         <v>56289</v>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654697</v>
+        <v>654716</v>
       </c>
       <c r="R6" t="n">
-        <v>6630371</v>
+        <v>6630357</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122249133</v>
+        <v>122249179</v>
       </c>
       <c r="B7" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,25 +1312,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654716</v>
+        <v>654759</v>
       </c>
       <c r="R7" t="n">
-        <v>6630357</v>
+        <v>6630339</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1414,14 +1414,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122249134</v>
+        <v>122249131</v>
       </c>
       <c r="B8" t="n">
         <v>56289</v>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654696</v>
+        <v>654693</v>
       </c>
       <c r="R8" t="n">
-        <v>6630370</v>
+        <v>6630371</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 49990-2023 artfynd.xlsx
+++ b/artfynd/A 49990-2023 artfynd.xlsx
@@ -1058,7 +1058,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122249139</v>
+        <v>122249131</v>
       </c>
       <c r="B5" t="n">
         <v>56289</v>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654697</v>
+        <v>654693</v>
       </c>
       <c r="R5" t="n">
         <v>6630371</v>
@@ -1179,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122249133</v>
+        <v>122249179</v>
       </c>
       <c r="B6" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,25 +1191,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654716</v>
+        <v>654759</v>
       </c>
       <c r="R6" t="n">
-        <v>6630357</v>
+        <v>6630339</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1293,17 +1293,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122249179</v>
+        <v>122249138</v>
       </c>
       <c r="B7" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,25 +1312,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654759</v>
+        <v>654707</v>
       </c>
       <c r="R7" t="n">
-        <v>6630339</v>
+        <v>6630361</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1414,14 +1414,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122249131</v>
+        <v>122249133</v>
       </c>
       <c r="B8" t="n">
         <v>56289</v>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654693</v>
+        <v>654716</v>
       </c>
       <c r="R8" t="n">
-        <v>6630371</v>
+        <v>6630357</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249138</v>
+        <v>122249139</v>
       </c>
       <c r="B9" t="n">
         <v>56289</v>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654707</v>
+        <v>654697</v>
       </c>
       <c r="R9" t="n">
-        <v>6630361</v>
+        <v>6630371</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 49990-2023 artfynd.xlsx
+++ b/artfynd/A 49990-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122249134</v>
+        <v>122249131</v>
       </c>
       <c r="B4" t="n">
         <v>56289</v>
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654696</v>
+        <v>654693</v>
       </c>
       <c r="R4" t="n">
-        <v>6630370</v>
+        <v>6630371</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122249131</v>
+        <v>122249134</v>
       </c>
       <c r="B5" t="n">
         <v>56289</v>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654693</v>
+        <v>654696</v>
       </c>
       <c r="R5" t="n">
-        <v>6630371</v>
+        <v>6630370</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1179,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122249179</v>
+        <v>122249139</v>
       </c>
       <c r="B6" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,25 +1191,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654759</v>
+        <v>654697</v>
       </c>
       <c r="R6" t="n">
-        <v>6630339</v>
+        <v>6630371</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249139</v>
+        <v>122249179</v>
       </c>
       <c r="B9" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,25 +1554,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654697</v>
+        <v>654759</v>
       </c>
       <c r="R9" t="n">
-        <v>6630371</v>
+        <v>6630339</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 49990-2023 artfynd.xlsx
+++ b/artfynd/A 49990-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122249131</v>
+        <v>122249138</v>
       </c>
       <c r="B4" t="n">
         <v>56289</v>
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654693</v>
+        <v>654707</v>
       </c>
       <c r="R4" t="n">
-        <v>6630371</v>
+        <v>6630361</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122249134</v>
+        <v>122249179</v>
       </c>
       <c r="B5" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,25 +1070,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654696</v>
+        <v>654759</v>
       </c>
       <c r="R5" t="n">
-        <v>6630370</v>
+        <v>6630339</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1172,14 +1172,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122249139</v>
+        <v>122249134</v>
       </c>
       <c r="B6" t="n">
         <v>56289</v>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654697</v>
+        <v>654696</v>
       </c>
       <c r="R6" t="n">
-        <v>6630371</v>
+        <v>6630370</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122249138</v>
+        <v>122249139</v>
       </c>
       <c r="B7" t="n">
         <v>56289</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654707</v>
+        <v>654697</v>
       </c>
       <c r="R7" t="n">
-        <v>6630361</v>
+        <v>6630371</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122249133</v>
+        <v>122249131</v>
       </c>
       <c r="B8" t="n">
         <v>56289</v>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654716</v>
+        <v>654693</v>
       </c>
       <c r="R8" t="n">
-        <v>6630357</v>
+        <v>6630371</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249179</v>
+        <v>122249133</v>
       </c>
       <c r="B9" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,25 +1554,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654759</v>
+        <v>654716</v>
       </c>
       <c r="R9" t="n">
-        <v>6630339</v>
+        <v>6630357</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 49990-2023 artfynd.xlsx
+++ b/artfynd/A 49990-2023 artfynd.xlsx
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122249138</v>
+        <v>122249133</v>
       </c>
       <c r="B4" t="n">
-        <v>56289</v>
+        <v>56290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654707</v>
+        <v>654716</v>
       </c>
       <c r="R4" t="n">
-        <v>6630361</v>
+        <v>6630357</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122249179</v>
+        <v>122249138</v>
       </c>
       <c r="B5" t="n">
-        <v>56275</v>
+        <v>56290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,25 +1070,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654759</v>
+        <v>654707</v>
       </c>
       <c r="R5" t="n">
-        <v>6630339</v>
+        <v>6630361</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1182,7 +1182,7 @@
         <v>122249134</v>
       </c>
       <c r="B6" t="n">
-        <v>56289</v>
+        <v>56290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122249139</v>
+        <v>122249179</v>
       </c>
       <c r="B7" t="n">
-        <v>56289</v>
+        <v>56276</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,25 +1312,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654697</v>
+        <v>654759</v>
       </c>
       <c r="R7" t="n">
-        <v>6630371</v>
+        <v>6630339</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Anna Eriksson, Björn Almkvist</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1424,7 +1424,7 @@
         <v>122249131</v>
       </c>
       <c r="B8" t="n">
-        <v>56289</v>
+        <v>56290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1542,10 +1542,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249133</v>
+        <v>122249139</v>
       </c>
       <c r="B9" t="n">
-        <v>56289</v>
+        <v>56290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654716</v>
+        <v>654697</v>
       </c>
       <c r="R9" t="n">
-        <v>6630357</v>
+        <v>6630371</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
